--- a/Organization_Template.xlsx
+++ b/Organization_Template.xlsx
@@ -1655,7 +1655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:I4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" bestFit="1" customWidth="1" style="23" min="1" max="1"/>
@@ -1706,11 +1706,6 @@
       </c>
       <c r="H2" s="32" t="inlineStr">
         <is>
-          <t>DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="I2" s="32" t="inlineStr">
-        <is>
           <t>NOTES</t>
         </is>
       </c>
@@ -1721,7 +1716,6 @@
       <c r="D3" s="6" t="n"/>
       <c r="F3" s="25" t="n"/>
       <c r="G3" s="25" t="n"/>
-      <c r="H3" s="25" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="25" t="n"/>
@@ -1729,7 +1723,6 @@
       <c r="D4" s="25" t="n"/>
       <c r="F4" s="25" t="n"/>
       <c r="G4" s="25" t="n"/>
-      <c r="H4" s="25" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
